--- a/검색어_맵핑.xlsx
+++ b/검색어_맵핑.xlsx
@@ -504,7 +504,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C85"/>
+  <dimension ref="A1:C86"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="17"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1622,26 +1622,21 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="2" t="n"/>
-      <c r="B68" s="2" t="n"/>
-      <c r="C68" s="2" t="n"/>
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>나조 이름</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>ようこそ恋愛創造ラボへ</t>
+        </is>
+      </c>
     </row>
     <row r="69">
-      <c r="A69" s="2" t="inlineStr">
-        <is>
-          <t>브랜드</t>
-        </is>
-      </c>
-      <c r="B69" s="2" t="inlineStr">
-        <is>
-          <t>tumbleweed</t>
-        </is>
-      </c>
-      <c r="C69" s="2" t="inlineStr">
-        <is>
-          <t>텀블위드, 탐블위도, 탐블위드</t>
-        </is>
-      </c>
+      <c r="A69" s="2" t="n"/>
+      <c r="B69" s="2" t="n"/>
+      <c r="C69" s="2" t="n"/>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -1651,12 +1646,12 @@
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>키이스케이프</t>
+          <t>tumbleweed</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>keyescape</t>
+          <t>텀블위드, 탐블위도, 탐블위드</t>
         </is>
       </c>
     </row>
@@ -1668,12 +1663,12 @@
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>NAZOxNAZO劇団</t>
-        </is>
-      </c>
-      <c r="C71" s="4" t="inlineStr">
-        <is>
-          <t>나조x나조극단, 나조x나조 극단, 나조나조극단, 나조x나조게키단, 나조나조게키단,나조,극단,게키단</t>
+          <t>키이스케이프</t>
+        </is>
+      </c>
+      <c r="C71" s="2" t="inlineStr">
+        <is>
+          <t>keyescape</t>
         </is>
       </c>
     </row>
@@ -1685,12 +1680,12 @@
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>MICHI</t>
-        </is>
-      </c>
-      <c r="C72" s="3" t="inlineStr">
-        <is>
-          <t>미치</t>
+          <t>NAZOxNAZO劇団</t>
+        </is>
+      </c>
+      <c r="C72" s="4" t="inlineStr">
+        <is>
+          <t>나조x나조극단, 나조x나조 극단, 나조나조극단, 나조x나조게키단, 나조나조게키단,나조,극단,게키단</t>
         </is>
       </c>
     </row>
@@ -1702,12 +1697,12 @@
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>ぐずりあ</t>
+          <t>MICHI</t>
         </is>
       </c>
       <c r="C73" s="3" t="inlineStr">
         <is>
-          <t>구스리아</t>
+          <t>미치</t>
         </is>
       </c>
     </row>
@@ -1719,12 +1714,12 @@
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>時解き</t>
+          <t>ぐずりあ</t>
         </is>
       </c>
       <c r="C74" s="3" t="inlineStr">
         <is>
-          <t>토키토키, tokitoki,토키,toki</t>
+          <t>구스리아</t>
         </is>
       </c>
     </row>
@@ -1736,12 +1731,12 @@
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>Mystery Lunch</t>
-        </is>
-      </c>
-      <c r="C75" s="4" t="inlineStr">
-        <is>
-          <t>미스테리 런치, 미스터리 런치, 미스테리런치, 미스터리런치,미스터리,미스테리,런치,점심</t>
+          <t>時解き</t>
+        </is>
+      </c>
+      <c r="C75" s="3" t="inlineStr">
+        <is>
+          <t>토키토키, tokitoki,토키,toki</t>
         </is>
       </c>
     </row>
@@ -1753,29 +1748,29 @@
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
+          <t>Mystery Lunch</t>
+        </is>
+      </c>
+      <c r="C76" s="4" t="inlineStr">
+        <is>
+          <t>미스테리 런치, 미스터리 런치, 미스테리런치, 미스터리런치,미스터리,미스테리,런치,점심</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr">
+        <is>
+          <t>브랜드</t>
+        </is>
+      </c>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
           <t>SCRAP</t>
         </is>
       </c>
-      <c r="C76" s="3" t="inlineStr">
+      <c r="C77" s="3" t="inlineStr">
         <is>
           <t>스크랩, 스크랍뿌, 스크랍부, 스크랏푸, 스크랏뿌, 스크렙</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" t="inlineStr">
-        <is>
-          <t>브랜드</t>
-        </is>
-      </c>
-      <c r="B77" t="inlineStr">
-        <is>
-          <t>SCRAP - Mystery For You</t>
-        </is>
-      </c>
-      <c r="C77" s="8" t="inlineStr">
-        <is>
-          <t>스크랩 - 미스터리 포유, 미스터리 포유, 미포유, Mystery For You, MFY</t>
         </is>
       </c>
     </row>
@@ -1787,12 +1782,12 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>4CE Dimension</t>
+          <t>SCRAP - Mystery For You</t>
         </is>
       </c>
       <c r="C78" s="8" t="inlineStr">
         <is>
-          <t>포스 디멘션, 포스 디멘젼</t>
+          <t>스크랩 - 미스터리 포유, 미스터리 포유, 미포유, Mystery For You, MFY</t>
         </is>
       </c>
     </row>
@@ -1804,12 +1799,12 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>AnotherVision</t>
+          <t>4CE Dimension</t>
         </is>
       </c>
       <c r="C79" s="8" t="inlineStr">
         <is>
-          <t>어나더비젼, 어나더비전, 어나더 비전, 어나더 비젼, 도쿄대 걔네</t>
+          <t>포스 디멘션, 포스 디멘젼</t>
         </is>
       </c>
     </row>
@@ -1821,12 +1816,12 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>xeoxy</t>
+          <t>AnotherVision</t>
         </is>
       </c>
       <c r="C80" s="8" t="inlineStr">
         <is>
-          <t>제옥시</t>
+          <t>어나더비젼, 어나더비전, 어나더 비전, 어나더 비젼, 도쿄대 걔네</t>
         </is>
       </c>
     </row>
@@ -1838,12 +1833,12 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>リドラ</t>
+          <t>xeoxy</t>
         </is>
       </c>
       <c r="C81" s="8" t="inlineStr">
         <is>
-          <t>리도라, 리들러</t>
+          <t>제옥시</t>
         </is>
       </c>
     </row>
@@ -1855,29 +1850,29 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>ねずみの巣</t>
+          <t>リドラ</t>
         </is>
       </c>
       <c r="C82" s="8" t="inlineStr">
         <is>
-          <t>쥐의굴, 쥐의 굴, 네즈미노 스, 쥐의둥지, 쥐의 둥지, 쥐의 보금자리, 쥐의보금자리, 쥐집, 쥐 집, 쥐의집, 쥐의 집</t>
+          <t>리도라, 리들러</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>나조 이름</t>
+          <t>브랜드</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>HIRAMEKI TRUMP</t>
-        </is>
-      </c>
-      <c r="C83" t="inlineStr">
-        <is>
-          <t>히라메키 트럼프, 히라메키트럼프, 히라메키, 트럼프</t>
+          <t>ねずみの巣</t>
+        </is>
+      </c>
+      <c r="C83" s="8" t="inlineStr">
+        <is>
+          <t>쥐의굴, 쥐의 굴, 네즈미노 스, 쥐의둥지, 쥐의 둥지, 쥐의 보금자리, 쥐의보금자리, 쥐집, 쥐 집, 쥐의집, 쥐의 집</t>
         </is>
       </c>
     </row>
@@ -1889,12 +1884,12 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>HIRAMEKI TRUMP RED</t>
+          <t>HIRAMEKI TRUMP</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>히라메키 트럼프 레드, 히라메키트럼프 레드, 히라메키트럼프레드, 히라메키 트럼프레드, 레드, 히라메키, 트럼프</t>
+          <t>히라메키 트럼프, 히라메키트럼프, 히라메키, 트럼프</t>
         </is>
       </c>
     </row>
@@ -1906,10 +1901,27 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
+          <t>HIRAMEKI TRUMP RED</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>히라메키 트럼프 레드, 히라메키트럼프 레드, 히라메키트럼프레드, 히라메키 트럼프레드, 레드, 히라메키, 트럼프</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>나조 이름</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
           <t>XI</t>
         </is>
       </c>
-      <c r="C85" t="inlineStr">
+      <c r="C86" t="inlineStr">
         <is>
           <t>일레븐, 엑스아이</t>
         </is>

--- a/검색어_맵핑.xlsx
+++ b/검색어_맵핑.xlsx
@@ -504,7 +504,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C86"/>
+  <dimension ref="A1:C87"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="17"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1634,26 +1634,21 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="2" t="n"/>
-      <c r="B69" s="2" t="n"/>
-      <c r="C69" s="2" t="n"/>
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>나조 이름</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>SCRAPPIESといっしょ</t>
+        </is>
+      </c>
     </row>
     <row r="70">
-      <c r="A70" s="2" t="inlineStr">
-        <is>
-          <t>브랜드</t>
-        </is>
-      </c>
-      <c r="B70" s="2" t="inlineStr">
-        <is>
-          <t>tumbleweed</t>
-        </is>
-      </c>
-      <c r="C70" s="2" t="inlineStr">
-        <is>
-          <t>텀블위드, 탐블위도, 탐블위드</t>
-        </is>
-      </c>
+      <c r="A70" s="2" t="n"/>
+      <c r="B70" s="2" t="n"/>
+      <c r="C70" s="2" t="n"/>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -1663,12 +1658,12 @@
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>키이스케이프</t>
+          <t>tumbleweed</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>keyescape</t>
+          <t>텀블위드, 탐블위도, 탐블위드</t>
         </is>
       </c>
     </row>
@@ -1680,12 +1675,12 @@
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>NAZOxNAZO劇団</t>
-        </is>
-      </c>
-      <c r="C72" s="4" t="inlineStr">
-        <is>
-          <t>나조x나조극단, 나조x나조 극단, 나조나조극단, 나조x나조게키단, 나조나조게키단,나조,극단,게키단</t>
+          <t>키이스케이프</t>
+        </is>
+      </c>
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>keyescape</t>
         </is>
       </c>
     </row>
@@ -1697,12 +1692,12 @@
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>MICHI</t>
-        </is>
-      </c>
-      <c r="C73" s="3" t="inlineStr">
-        <is>
-          <t>미치</t>
+          <t>NAZOxNAZO劇団</t>
+        </is>
+      </c>
+      <c r="C73" s="4" t="inlineStr">
+        <is>
+          <t>나조x나조극단, 나조x나조 극단, 나조나조극단, 나조x나조게키단, 나조나조게키단,나조,극단,게키단</t>
         </is>
       </c>
     </row>
@@ -1714,12 +1709,12 @@
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>ぐずりあ</t>
+          <t>MICHI</t>
         </is>
       </c>
       <c r="C74" s="3" t="inlineStr">
         <is>
-          <t>구스리아</t>
+          <t>미치</t>
         </is>
       </c>
     </row>
@@ -1731,12 +1726,12 @@
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>時解き</t>
+          <t>ぐずりあ</t>
         </is>
       </c>
       <c r="C75" s="3" t="inlineStr">
         <is>
-          <t>토키토키, tokitoki,토키,toki</t>
+          <t>구스리아</t>
         </is>
       </c>
     </row>
@@ -1748,12 +1743,12 @@
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>Mystery Lunch</t>
-        </is>
-      </c>
-      <c r="C76" s="4" t="inlineStr">
-        <is>
-          <t>미스테리 런치, 미스터리 런치, 미스테리런치, 미스터리런치,미스터리,미스테리,런치,점심</t>
+          <t>時解き</t>
+        </is>
+      </c>
+      <c r="C76" s="3" t="inlineStr">
+        <is>
+          <t>토키토키, tokitoki,토키,toki</t>
         </is>
       </c>
     </row>
@@ -1765,29 +1760,29 @@
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
+          <t>Mystery Lunch</t>
+        </is>
+      </c>
+      <c r="C77" s="4" t="inlineStr">
+        <is>
+          <t>미스테리 런치, 미스터리 런치, 미스테리런치, 미스터리런치,미스터리,미스테리,런치,점심</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr">
+        <is>
+          <t>브랜드</t>
+        </is>
+      </c>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
           <t>SCRAP</t>
         </is>
       </c>
-      <c r="C77" s="3" t="inlineStr">
+      <c r="C78" s="3" t="inlineStr">
         <is>
           <t>스크랩, 스크랍뿌, 스크랍부, 스크랏푸, 스크랏뿌, 스크렙</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" t="inlineStr">
-        <is>
-          <t>브랜드</t>
-        </is>
-      </c>
-      <c r="B78" t="inlineStr">
-        <is>
-          <t>SCRAP - Mystery For You</t>
-        </is>
-      </c>
-      <c r="C78" s="8" t="inlineStr">
-        <is>
-          <t>스크랩 - 미스터리 포유, 미스터리 포유, 미포유, Mystery For You, MFY</t>
         </is>
       </c>
     </row>
@@ -1799,12 +1794,12 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>4CE Dimension</t>
+          <t>SCRAP - Mystery For You</t>
         </is>
       </c>
       <c r="C79" s="8" t="inlineStr">
         <is>
-          <t>포스 디멘션, 포스 디멘젼</t>
+          <t>스크랩 - 미스터리 포유, 미스터리 포유, 미포유, Mystery For You, MFY</t>
         </is>
       </c>
     </row>
@@ -1816,12 +1811,12 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>AnotherVision</t>
+          <t>4CE Dimension</t>
         </is>
       </c>
       <c r="C80" s="8" t="inlineStr">
         <is>
-          <t>어나더비젼, 어나더비전, 어나더 비전, 어나더 비젼, 도쿄대 걔네</t>
+          <t>포스 디멘션, 포스 디멘젼</t>
         </is>
       </c>
     </row>
@@ -1833,12 +1828,12 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>xeoxy</t>
+          <t>AnotherVision</t>
         </is>
       </c>
       <c r="C81" s="8" t="inlineStr">
         <is>
-          <t>제옥시</t>
+          <t>어나더비젼, 어나더비전, 어나더 비전, 어나더 비젼, 도쿄대 걔네</t>
         </is>
       </c>
     </row>
@@ -1850,12 +1845,12 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>リドラ</t>
+          <t>xeoxy</t>
         </is>
       </c>
       <c r="C82" s="8" t="inlineStr">
         <is>
-          <t>리도라, 리들러</t>
+          <t>제옥시</t>
         </is>
       </c>
     </row>
@@ -1867,29 +1862,29 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>ねずみの巣</t>
+          <t>リドラ</t>
         </is>
       </c>
       <c r="C83" s="8" t="inlineStr">
         <is>
-          <t>쥐의굴, 쥐의 굴, 네즈미노 스, 쥐의둥지, 쥐의 둥지, 쥐의 보금자리, 쥐의보금자리, 쥐집, 쥐 집, 쥐의집, 쥐의 집</t>
+          <t>리도라, 리들러</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>나조 이름</t>
+          <t>브랜드</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>HIRAMEKI TRUMP</t>
-        </is>
-      </c>
-      <c r="C84" t="inlineStr">
-        <is>
-          <t>히라메키 트럼프, 히라메키트럼프, 히라메키, 트럼프</t>
+          <t>ねずみの巣</t>
+        </is>
+      </c>
+      <c r="C84" s="8" t="inlineStr">
+        <is>
+          <t>쥐의굴, 쥐의 굴, 네즈미노 스, 쥐의둥지, 쥐의 둥지, 쥐의 보금자리, 쥐의보금자리, 쥐집, 쥐 집, 쥐의집, 쥐의 집</t>
         </is>
       </c>
     </row>
@@ -1901,12 +1896,12 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>HIRAMEKI TRUMP RED</t>
+          <t>HIRAMEKI TRUMP</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>히라메키 트럼프 레드, 히라메키트럼프 레드, 히라메키트럼프레드, 히라메키 트럼프레드, 레드, 히라메키, 트럼프</t>
+          <t>히라메키 트럼프, 히라메키트럼프, 히라메키, 트럼프</t>
         </is>
       </c>
     </row>
@@ -1918,10 +1913,27 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
+          <t>HIRAMEKI TRUMP RED</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>히라메키 트럼프 레드, 히라메키트럼프 레드, 히라메키트럼프레드, 히라메키 트럼프레드, 레드, 히라메키, 트럼프</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>나조 이름</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
           <t>XI</t>
         </is>
       </c>
-      <c r="C86" t="inlineStr">
+      <c r="C87" t="inlineStr">
         <is>
           <t>일레븐, 엑스아이</t>
         </is>

--- a/검색어_맵핑.xlsx
+++ b/검색어_맵핑.xlsx
@@ -504,7 +504,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C87"/>
+  <dimension ref="A1:C94"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="17"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1646,94 +1646,69 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="2" t="n"/>
-      <c r="B70" s="2" t="n"/>
-      <c r="C70" s="2" t="n"/>
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>나조 이름</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>棘 -おどろ-</t>
+        </is>
+      </c>
     </row>
     <row r="71">
-      <c r="A71" s="2" t="inlineStr">
-        <is>
-          <t>브랜드</t>
-        </is>
-      </c>
-      <c r="B71" s="2" t="inlineStr">
-        <is>
-          <t>tumbleweed</t>
-        </is>
-      </c>
-      <c r="C71" s="2" t="inlineStr">
-        <is>
-          <t>텀블위드, 탐블위도, 탐블위드</t>
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>나조 이름</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>電脳都市Acrossの謎</t>
         </is>
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="2" t="inlineStr">
-        <is>
-          <t>브랜드</t>
-        </is>
-      </c>
-      <c r="B72" s="2" t="inlineStr">
-        <is>
-          <t>키이스케이프</t>
-        </is>
-      </c>
-      <c r="C72" s="2" t="inlineStr">
-        <is>
-          <t>keyescape</t>
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>나조 이름</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>レコード</t>
         </is>
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="2" t="inlineStr">
-        <is>
-          <t>브랜드</t>
-        </is>
-      </c>
-      <c r="B73" s="2" t="inlineStr">
-        <is>
-          <t>NAZOxNAZO劇団</t>
-        </is>
-      </c>
-      <c r="C73" s="4" t="inlineStr">
-        <is>
-          <t>나조x나조극단, 나조x나조 극단, 나조나조극단, 나조x나조게키단, 나조나조게키단,나조,극단,게키단</t>
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>나조 이름</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>世界を救え SCRAPPIES</t>
         </is>
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="2" t="inlineStr">
-        <is>
-          <t>브랜드</t>
-        </is>
-      </c>
-      <c r="B74" s="2" t="inlineStr">
-        <is>
-          <t>MICHI</t>
-        </is>
-      </c>
-      <c r="C74" s="3" t="inlineStr">
-        <is>
-          <t>미치</t>
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>나조 이름</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>No image Enigma</t>
         </is>
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="2" t="inlineStr">
-        <is>
-          <t>브랜드</t>
-        </is>
-      </c>
-      <c r="B75" s="2" t="inlineStr">
-        <is>
-          <t>ぐずりあ</t>
-        </is>
-      </c>
-      <c r="C75" s="3" t="inlineStr">
-        <is>
-          <t>구스리아</t>
-        </is>
-      </c>
+      <c r="A75" s="2" t="n"/>
+      <c r="B75" s="2" t="n"/>
+      <c r="C75" s="2" t="n"/>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -1743,12 +1718,12 @@
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>時解き</t>
-        </is>
-      </c>
-      <c r="C76" s="3" t="inlineStr">
-        <is>
-          <t>토키토키, tokitoki,토키,toki</t>
+          <t>tumbleweed</t>
+        </is>
+      </c>
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t>텀블위드, 탐블위도, 탐블위드</t>
         </is>
       </c>
     </row>
@@ -1760,12 +1735,12 @@
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>Mystery Lunch</t>
-        </is>
-      </c>
-      <c r="C77" s="4" t="inlineStr">
-        <is>
-          <t>미스테리 런치, 미스터리 런치, 미스테리런치, 미스터리런치,미스터리,미스테리,런치,점심</t>
+          <t>키이스케이프</t>
+        </is>
+      </c>
+      <c r="C77" s="2" t="inlineStr">
+        <is>
+          <t>keyescape</t>
         </is>
       </c>
     </row>
@@ -1777,97 +1752,97 @@
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
+          <t>NAZOxNAZO劇団</t>
+        </is>
+      </c>
+      <c r="C78" s="4" t="inlineStr">
+        <is>
+          <t>나조x나조극단, 나조x나조 극단, 나조나조극단, 나조x나조게키단, 나조나조게키단,나조,극단,게키단</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr">
+        <is>
+          <t>브랜드</t>
+        </is>
+      </c>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
+          <t>MICHI</t>
+        </is>
+      </c>
+      <c r="C79" s="3" t="inlineStr">
+        <is>
+          <t>미치</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr">
+        <is>
+          <t>브랜드</t>
+        </is>
+      </c>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
+          <t>ぐずりあ</t>
+        </is>
+      </c>
+      <c r="C80" s="3" t="inlineStr">
+        <is>
+          <t>구스리아</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr">
+        <is>
+          <t>브랜드</t>
+        </is>
+      </c>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
+          <t>時解き</t>
+        </is>
+      </c>
+      <c r="C81" s="3" t="inlineStr">
+        <is>
+          <t>토키토키, tokitoki,토키,toki</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr">
+        <is>
+          <t>브랜드</t>
+        </is>
+      </c>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
+          <t>Mystery Lunch</t>
+        </is>
+      </c>
+      <c r="C82" s="4" t="inlineStr">
+        <is>
+          <t>미스테리 런치, 미스터리 런치, 미스테리런치, 미스터리런치,미스터리,미스테리,런치,점심</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr">
+        <is>
+          <t>브랜드</t>
+        </is>
+      </c>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
           <t>SCRAP</t>
         </is>
       </c>
-      <c r="C78" s="3" t="inlineStr">
+      <c r="C83" s="3" t="inlineStr">
         <is>
           <t>스크랩, 스크랍뿌, 스크랍부, 스크랏푸, 스크랏뿌, 스크렙</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" t="inlineStr">
-        <is>
-          <t>브랜드</t>
-        </is>
-      </c>
-      <c r="B79" t="inlineStr">
-        <is>
-          <t>SCRAP - Mystery For You</t>
-        </is>
-      </c>
-      <c r="C79" s="8" t="inlineStr">
-        <is>
-          <t>스크랩 - 미스터리 포유, 미스터리 포유, 미포유, Mystery For You, MFY</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" t="inlineStr">
-        <is>
-          <t>브랜드</t>
-        </is>
-      </c>
-      <c r="B80" t="inlineStr">
-        <is>
-          <t>4CE Dimension</t>
-        </is>
-      </c>
-      <c r="C80" s="8" t="inlineStr">
-        <is>
-          <t>포스 디멘션, 포스 디멘젼</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" t="inlineStr">
-        <is>
-          <t>브랜드</t>
-        </is>
-      </c>
-      <c r="B81" t="inlineStr">
-        <is>
-          <t>AnotherVision</t>
-        </is>
-      </c>
-      <c r="C81" s="8" t="inlineStr">
-        <is>
-          <t>어나더비젼, 어나더비전, 어나더 비전, 어나더 비젼, 도쿄대 걔네</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" t="inlineStr">
-        <is>
-          <t>브랜드</t>
-        </is>
-      </c>
-      <c r="B82" t="inlineStr">
-        <is>
-          <t>xeoxy</t>
-        </is>
-      </c>
-      <c r="C82" s="8" t="inlineStr">
-        <is>
-          <t>제옥시</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" t="inlineStr">
-        <is>
-          <t>브랜드</t>
-        </is>
-      </c>
-      <c r="B83" t="inlineStr">
-        <is>
-          <t>リドラ</t>
-        </is>
-      </c>
-      <c r="C83" s="8" t="inlineStr">
-        <is>
-          <t>리도라, 리들러</t>
         </is>
       </c>
     </row>
@@ -1879,63 +1854,172 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>ねずみの巣</t>
+          <t>SCRAP - Mystery For You</t>
         </is>
       </c>
       <c r="C84" s="8" t="inlineStr">
         <is>
-          <t>쥐의굴, 쥐의 굴, 네즈미노 스, 쥐의둥지, 쥐의 둥지, 쥐의 보금자리, 쥐의보금자리, 쥐집, 쥐 집, 쥐의집, 쥐의 집</t>
+          <t>스크랩 - 미스터리 포유, 미스터리 포유, 미포유, Mystery For You, MFY</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>나조 이름</t>
+          <t>브랜드</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>HIRAMEKI TRUMP</t>
-        </is>
-      </c>
-      <c r="C85" t="inlineStr">
-        <is>
-          <t>히라메키 트럼프, 히라메키트럼프, 히라메키, 트럼프</t>
+          <t>4CE Dimension</t>
+        </is>
+      </c>
+      <c r="C85" s="8" t="inlineStr">
+        <is>
+          <t>포스 디멘션, 포스 디멘젼</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>나조 이름</t>
+          <t>브랜드</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>HIRAMEKI TRUMP RED</t>
-        </is>
-      </c>
-      <c r="C86" t="inlineStr">
-        <is>
-          <t>히라메키 트럼프 레드, 히라메키트럼프 레드, 히라메키트럼프레드, 히라메키 트럼프레드, 레드, 히라메키, 트럼프</t>
+          <t>AnotherVision</t>
+        </is>
+      </c>
+      <c r="C86" s="8" t="inlineStr">
+        <is>
+          <t>어나더비젼, 어나더비전, 어나더 비전, 어나더 비젼, 도쿄대 걔네</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>나조 이름</t>
+          <t>브랜드</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
+          <t>xeoxy</t>
+        </is>
+      </c>
+      <c r="C87" s="8" t="inlineStr">
+        <is>
+          <t>제옥시</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>브랜드</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>リドラ</t>
+        </is>
+      </c>
+      <c r="C88" s="8" t="inlineStr">
+        <is>
+          <t>리도라, 리들러</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>브랜드</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>ねずみの巣</t>
+        </is>
+      </c>
+      <c r="C89" s="8" t="inlineStr">
+        <is>
+          <t>쥐의굴, 쥐의 굴, 네즈미노 스, 쥐의둥지, 쥐의 둥지, 쥐의 보금자리, 쥐의보금자리, 쥐집, 쥐 집, 쥐의집, 쥐의 집</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>나조 이름</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>HIRAMEKI TRUMP</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>히라메키 트럼프, 히라메키트럼프, 히라메키, 트럼프</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>나조 이름</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>HIRAMEKI TRUMP RED</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>히라메키 트럼프 레드, 히라메키트럼프 레드, 히라메키트럼프레드, 히라메키 트럼프레드, 레드, 히라메키, 트럼프</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>나조 이름</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
           <t>XI</t>
         </is>
       </c>
-      <c r="C87" t="inlineStr">
+      <c r="C92" t="inlineStr">
         <is>
           <t>일레븐, 엑스아이</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>브랜드</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>街ハック！</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>브랜드</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>ナゾトキアドベンチャー</t>
         </is>
       </c>
     </row>

--- a/검색어_맵핑.xlsx
+++ b/검색어_맵핑.xlsx
@@ -504,7 +504,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C94"/>
+  <dimension ref="A1:C95"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="17"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1706,26 +1706,21 @@
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="2" t="n"/>
-      <c r="B75" s="2" t="n"/>
-      <c r="C75" s="2" t="n"/>
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>나조 이름</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>HOLE</t>
+        </is>
+      </c>
     </row>
     <row r="76">
-      <c r="A76" s="2" t="inlineStr">
-        <is>
-          <t>브랜드</t>
-        </is>
-      </c>
-      <c r="B76" s="2" t="inlineStr">
-        <is>
-          <t>tumbleweed</t>
-        </is>
-      </c>
-      <c r="C76" s="2" t="inlineStr">
-        <is>
-          <t>텀블위드, 탐블위도, 탐블위드</t>
-        </is>
-      </c>
+      <c r="A76" s="2" t="n"/>
+      <c r="B76" s="2" t="n"/>
+      <c r="C76" s="2" t="n"/>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -1735,12 +1730,12 @@
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>키이스케이프</t>
+          <t>tumbleweed</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
         <is>
-          <t>keyescape</t>
+          <t>텀블위드, 탐블위도, 탐블위드</t>
         </is>
       </c>
     </row>
@@ -1752,12 +1747,12 @@
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>NAZOxNAZO劇団</t>
-        </is>
-      </c>
-      <c r="C78" s="4" t="inlineStr">
-        <is>
-          <t>나조x나조극단, 나조x나조 극단, 나조나조극단, 나조x나조게키단, 나조나조게키단,나조,극단,게키단</t>
+          <t>키이스케이프</t>
+        </is>
+      </c>
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>keyescape</t>
         </is>
       </c>
     </row>
@@ -1769,12 +1764,12 @@
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>MICHI</t>
-        </is>
-      </c>
-      <c r="C79" s="3" t="inlineStr">
-        <is>
-          <t>미치</t>
+          <t>NAZOxNAZO劇団</t>
+        </is>
+      </c>
+      <c r="C79" s="4" t="inlineStr">
+        <is>
+          <t>나조x나조극단, 나조x나조 극단, 나조나조극단, 나조x나조게키단, 나조나조게키단,나조,극단,게키단</t>
         </is>
       </c>
     </row>
@@ -1786,12 +1781,12 @@
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>ぐずりあ</t>
+          <t>MICHI</t>
         </is>
       </c>
       <c r="C80" s="3" t="inlineStr">
         <is>
-          <t>구스리아</t>
+          <t>미치</t>
         </is>
       </c>
     </row>
@@ -1803,12 +1798,12 @@
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>時解き</t>
+          <t>ぐずりあ</t>
         </is>
       </c>
       <c r="C81" s="3" t="inlineStr">
         <is>
-          <t>토키토키, tokitoki,토키,toki</t>
+          <t>구스리아</t>
         </is>
       </c>
     </row>
@@ -1820,12 +1815,12 @@
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>Mystery Lunch</t>
-        </is>
-      </c>
-      <c r="C82" s="4" t="inlineStr">
-        <is>
-          <t>미스테리 런치, 미스터리 런치, 미스테리런치, 미스터리런치,미스터리,미스테리,런치,점심</t>
+          <t>時解き</t>
+        </is>
+      </c>
+      <c r="C82" s="3" t="inlineStr">
+        <is>
+          <t>토키토키, tokitoki,토키,toki</t>
         </is>
       </c>
     </row>
@@ -1837,29 +1832,29 @@
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
+          <t>Mystery Lunch</t>
+        </is>
+      </c>
+      <c r="C83" s="4" t="inlineStr">
+        <is>
+          <t>미스테리 런치, 미스터리 런치, 미스테리런치, 미스터리런치,미스터리,미스테리,런치,점심</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr">
+        <is>
+          <t>브랜드</t>
+        </is>
+      </c>
+      <c r="B84" s="2" t="inlineStr">
+        <is>
           <t>SCRAP</t>
         </is>
       </c>
-      <c r="C83" s="3" t="inlineStr">
+      <c r="C84" s="3" t="inlineStr">
         <is>
           <t>스크랩, 스크랍뿌, 스크랍부, 스크랏푸, 스크랏뿌, 스크렙</t>
-        </is>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" t="inlineStr">
-        <is>
-          <t>브랜드</t>
-        </is>
-      </c>
-      <c r="B84" t="inlineStr">
-        <is>
-          <t>SCRAP - Mystery For You</t>
-        </is>
-      </c>
-      <c r="C84" s="8" t="inlineStr">
-        <is>
-          <t>스크랩 - 미스터리 포유, 미스터리 포유, 미포유, Mystery For You, MFY</t>
         </is>
       </c>
     </row>
@@ -1871,12 +1866,12 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>4CE Dimension</t>
+          <t>SCRAP - Mystery For You</t>
         </is>
       </c>
       <c r="C85" s="8" t="inlineStr">
         <is>
-          <t>포스 디멘션, 포스 디멘젼</t>
+          <t>스크랩 - 미스터리 포유, 미스터리 포유, 미포유, Mystery For You, MFY</t>
         </is>
       </c>
     </row>
@@ -1888,12 +1883,12 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>AnotherVision</t>
+          <t>4CE Dimension</t>
         </is>
       </c>
       <c r="C86" s="8" t="inlineStr">
         <is>
-          <t>어나더비젼, 어나더비전, 어나더 비전, 어나더 비젼, 도쿄대 걔네</t>
+          <t>포스 디멘션, 포스 디멘젼</t>
         </is>
       </c>
     </row>
@@ -1905,12 +1900,12 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>xeoxy</t>
+          <t>AnotherVision</t>
         </is>
       </c>
       <c r="C87" s="8" t="inlineStr">
         <is>
-          <t>제옥시</t>
+          <t>어나더비젼, 어나더비전, 어나더 비전, 어나더 비젼, 도쿄대 걔네</t>
         </is>
       </c>
     </row>
@@ -1922,12 +1917,12 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>リドラ</t>
+          <t>xeoxy</t>
         </is>
       </c>
       <c r="C88" s="8" t="inlineStr">
         <is>
-          <t>리도라, 리들러</t>
+          <t>제옥시</t>
         </is>
       </c>
     </row>
@@ -1939,29 +1934,29 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>ねずみの巣</t>
+          <t>リドラ</t>
         </is>
       </c>
       <c r="C89" s="8" t="inlineStr">
         <is>
-          <t>쥐의굴, 쥐의 굴, 네즈미노 스, 쥐의둥지, 쥐의 둥지, 쥐의 보금자리, 쥐의보금자리, 쥐집, 쥐 집, 쥐의집, 쥐의 집</t>
+          <t>리도라, 리들러</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>나조 이름</t>
+          <t>브랜드</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>HIRAMEKI TRUMP</t>
-        </is>
-      </c>
-      <c r="C90" t="inlineStr">
-        <is>
-          <t>히라메키 트럼프, 히라메키트럼프, 히라메키, 트럼프</t>
+          <t>ねずみの巣</t>
+        </is>
+      </c>
+      <c r="C90" s="8" t="inlineStr">
+        <is>
+          <t>쥐의굴, 쥐의 굴, 네즈미노 스, 쥐의둥지, 쥐의 둥지, 쥐의 보금자리, 쥐의보금자리, 쥐집, 쥐 집, 쥐의집, 쥐의 집</t>
         </is>
       </c>
     </row>
@@ -1973,12 +1968,12 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>HIRAMEKI TRUMP RED</t>
+          <t>HIRAMEKI TRUMP</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>히라메키 트럼프 레드, 히라메키트럼프 레드, 히라메키트럼프레드, 히라메키 트럼프레드, 레드, 히라메키, 트럼프</t>
+          <t>히라메키 트럼프, 히라메키트럼프, 히라메키, 트럼프</t>
         </is>
       </c>
     </row>
@@ -1990,24 +1985,29 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>XI</t>
+          <t>HIRAMEKI TRUMP RED</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>일레븐, 엑스아이</t>
+          <t>히라메키 트럼프 레드, 히라메키트럼프 레드, 히라메키트럼프레드, 히라메키 트럼프레드, 레드, 히라메키, 트럼프</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>브랜드</t>
+          <t>나조 이름</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>街ハック！</t>
+          <t>XI</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>일레븐, 엑스아이</t>
         </is>
       </c>
     </row>
@@ -2018,6 +2018,18 @@
         </is>
       </c>
       <c r="B94" t="inlineStr">
+        <is>
+          <t>街ハック！</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>브랜드</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
         <is>
           <t>ナゾトキアドベンチャー</t>
         </is>

--- a/검색어_맵핑.xlsx
+++ b/검색어_맵핑.xlsx
@@ -504,7 +504,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C95"/>
+  <dimension ref="A1:C97"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="17"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1718,43 +1718,33 @@
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="2" t="n"/>
-      <c r="B76" s="2" t="n"/>
-      <c r="C76" s="2" t="n"/>
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>나조 이름</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>Unlock! 参加者限定ナゾ</t>
+        </is>
+      </c>
     </row>
     <row r="77">
-      <c r="A77" s="2" t="inlineStr">
-        <is>
-          <t>브랜드</t>
-        </is>
-      </c>
-      <c r="B77" s="2" t="inlineStr">
-        <is>
-          <t>tumbleweed</t>
-        </is>
-      </c>
-      <c r="C77" s="2" t="inlineStr">
-        <is>
-          <t>텀블위드, 탐블위도, 탐블위드</t>
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>나조 이름</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>LIMINAL ESCAPE 参加者限定持ち帰りナゾ</t>
         </is>
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="2" t="inlineStr">
-        <is>
-          <t>브랜드</t>
-        </is>
-      </c>
-      <c r="B78" s="2" t="inlineStr">
-        <is>
-          <t>키이스케이프</t>
-        </is>
-      </c>
-      <c r="C78" s="2" t="inlineStr">
-        <is>
-          <t>keyescape</t>
-        </is>
-      </c>
+      <c r="A78" s="2" t="n"/>
+      <c r="B78" s="2" t="n"/>
+      <c r="C78" s="2" t="n"/>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -1764,12 +1754,12 @@
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>NAZOxNAZO劇団</t>
-        </is>
-      </c>
-      <c r="C79" s="4" t="inlineStr">
-        <is>
-          <t>나조x나조극단, 나조x나조 극단, 나조나조극단, 나조x나조게키단, 나조나조게키단,나조,극단,게키단</t>
+          <t>tumbleweed</t>
+        </is>
+      </c>
+      <c r="C79" s="2" t="inlineStr">
+        <is>
+          <t>텀블위드, 탐블위도, 탐블위드</t>
         </is>
       </c>
     </row>
@@ -1781,12 +1771,12 @@
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>MICHI</t>
-        </is>
-      </c>
-      <c r="C80" s="3" t="inlineStr">
-        <is>
-          <t>미치</t>
+          <t>키이스케이프</t>
+        </is>
+      </c>
+      <c r="C80" s="2" t="inlineStr">
+        <is>
+          <t>keyescape</t>
         </is>
       </c>
     </row>
@@ -1798,12 +1788,12 @@
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>ぐずりあ</t>
-        </is>
-      </c>
-      <c r="C81" s="3" t="inlineStr">
-        <is>
-          <t>구스리아</t>
+          <t>NAZOxNAZO劇団</t>
+        </is>
+      </c>
+      <c r="C81" s="4" t="inlineStr">
+        <is>
+          <t>나조x나조극단, 나조x나조 극단, 나조나조극단, 나조x나조게키단, 나조나조게키단,나조,극단,게키단</t>
         </is>
       </c>
     </row>
@@ -1815,12 +1805,12 @@
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>時解き</t>
+          <t>MICHI</t>
         </is>
       </c>
       <c r="C82" s="3" t="inlineStr">
         <is>
-          <t>토키토키, tokitoki,토키,toki</t>
+          <t>미치</t>
         </is>
       </c>
     </row>
@@ -1832,12 +1822,12 @@
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>Mystery Lunch</t>
-        </is>
-      </c>
-      <c r="C83" s="4" t="inlineStr">
-        <is>
-          <t>미스테리 런치, 미스터리 런치, 미스테리런치, 미스터리런치,미스터리,미스테리,런치,점심</t>
+          <t>ぐずりあ</t>
+        </is>
+      </c>
+      <c r="C83" s="3" t="inlineStr">
+        <is>
+          <t>구스리아</t>
         </is>
       </c>
     </row>
@@ -1849,46 +1839,46 @@
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
+          <t>時解き</t>
+        </is>
+      </c>
+      <c r="C84" s="3" t="inlineStr">
+        <is>
+          <t>토키토키, tokitoki,토키,toki</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="inlineStr">
+        <is>
+          <t>브랜드</t>
+        </is>
+      </c>
+      <c r="B85" s="2" t="inlineStr">
+        <is>
+          <t>Mystery Lunch</t>
+        </is>
+      </c>
+      <c r="C85" s="4" t="inlineStr">
+        <is>
+          <t>미스테리 런치, 미스터리 런치, 미스테리런치, 미스터리런치,미스터리,미스테리,런치,점심</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr">
+        <is>
+          <t>브랜드</t>
+        </is>
+      </c>
+      <c r="B86" s="2" t="inlineStr">
+        <is>
           <t>SCRAP</t>
         </is>
       </c>
-      <c r="C84" s="3" t="inlineStr">
+      <c r="C86" s="3" t="inlineStr">
         <is>
           <t>스크랩, 스크랍뿌, 스크랍부, 스크랏푸, 스크랏뿌, 스크렙</t>
-        </is>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" t="inlineStr">
-        <is>
-          <t>브랜드</t>
-        </is>
-      </c>
-      <c r="B85" t="inlineStr">
-        <is>
-          <t>SCRAP - Mystery For You</t>
-        </is>
-      </c>
-      <c r="C85" s="8" t="inlineStr">
-        <is>
-          <t>스크랩 - 미스터리 포유, 미스터리 포유, 미포유, Mystery For You, MFY</t>
-        </is>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" t="inlineStr">
-        <is>
-          <t>브랜드</t>
-        </is>
-      </c>
-      <c r="B86" t="inlineStr">
-        <is>
-          <t>4CE Dimension</t>
-        </is>
-      </c>
-      <c r="C86" s="8" t="inlineStr">
-        <is>
-          <t>포스 디멘션, 포스 디멘젼</t>
         </is>
       </c>
     </row>
@@ -1900,12 +1890,12 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>AnotherVision</t>
+          <t>SCRAP - Mystery For You</t>
         </is>
       </c>
       <c r="C87" s="8" t="inlineStr">
         <is>
-          <t>어나더비젼, 어나더비전, 어나더 비전, 어나더 비젼, 도쿄대 걔네</t>
+          <t>스크랩 - 미스터리 포유, 미스터리 포유, 미포유, Mystery For You, MFY</t>
         </is>
       </c>
     </row>
@@ -1917,12 +1907,12 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>xeoxy</t>
+          <t>4CE Dimension</t>
         </is>
       </c>
       <c r="C88" s="8" t="inlineStr">
         <is>
-          <t>제옥시</t>
+          <t>포스 디멘션, 포스 디멘젼</t>
         </is>
       </c>
     </row>
@@ -1934,12 +1924,12 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>リドラ</t>
+          <t>AnotherVision</t>
         </is>
       </c>
       <c r="C89" s="8" t="inlineStr">
         <is>
-          <t>리도라, 리들러</t>
+          <t>어나더비젼, 어나더비전, 어나더 비전, 어나더 비젼, 도쿄대 걔네</t>
         </is>
       </c>
     </row>
@@ -1951,46 +1941,46 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>ねずみの巣</t>
+          <t>xeoxy</t>
         </is>
       </c>
       <c r="C90" s="8" t="inlineStr">
         <is>
-          <t>쥐의굴, 쥐의 굴, 네즈미노 스, 쥐의둥지, 쥐의 둥지, 쥐의 보금자리, 쥐의보금자리, 쥐집, 쥐 집, 쥐의집, 쥐의 집</t>
+          <t>제옥시</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>나조 이름</t>
+          <t>브랜드</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>HIRAMEKI TRUMP</t>
-        </is>
-      </c>
-      <c r="C91" t="inlineStr">
-        <is>
-          <t>히라메키 트럼프, 히라메키트럼프, 히라메키, 트럼프</t>
+          <t>リドラ</t>
+        </is>
+      </c>
+      <c r="C91" s="8" t="inlineStr">
+        <is>
+          <t>리도라, 리들러</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>나조 이름</t>
+          <t>브랜드</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>HIRAMEKI TRUMP RED</t>
-        </is>
-      </c>
-      <c r="C92" t="inlineStr">
-        <is>
-          <t>히라메키 트럼프 레드, 히라메키트럼프 레드, 히라메키트럼프레드, 히라메키 트럼프레드, 레드, 히라메키, 트럼프</t>
+          <t>ねずみの巣</t>
+        </is>
+      </c>
+      <c r="C92" s="8" t="inlineStr">
+        <is>
+          <t>쥐의굴, 쥐의 굴, 네즈미노 스, 쥐의둥지, 쥐의 둥지, 쥐의 보금자리, 쥐의보금자리, 쥐집, 쥐 집, 쥐의집, 쥐의 집</t>
         </is>
       </c>
     </row>
@@ -2002,34 +1992,68 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>XI</t>
+          <t>HIRAMEKI TRUMP</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>일레븐, 엑스아이</t>
+          <t>히라메키 트럼프, 히라메키트럼프, 히라메키, 트럼프</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>브랜드</t>
+          <t>나조 이름</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>街ハック！</t>
+          <t>HIRAMEKI TRUMP RED</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>히라메키 트럼프 레드, 히라메키트럼프 레드, 히라메키트럼프레드, 히라메키 트럼프레드, 레드, 히라메키, 트럼프</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
+          <t>나조 이름</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>XI</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>일레븐, 엑스아이</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
           <t>브랜드</t>
         </is>
       </c>
-      <c r="B95" t="inlineStr">
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>街ハック！</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>브랜드</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
         <is>
           <t>ナゾトキアドベンチャー</t>
         </is>
